--- a/app/data/contacts.xlsx
+++ b/app/data/contacts.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>email</t>
   </si>
@@ -50,13 +50,19 @@
     <t>Егорьевск</t>
   </si>
   <si>
+    <t>МоеИмя</t>
+  </si>
+  <si>
     <t>xena02@mail.ru</t>
   </si>
   <si>
     <t>ksh.anisik@mail.ru</t>
   </si>
   <si>
-    <t>Ксюша</t>
+    <t>Солис</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Форум" </t>
   </si>
 </sst>
 </file>
@@ -385,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -407,10 +413,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -421,7 +427,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -431,10 +437,29 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -468,11 +493,118 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
     <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
